--- a/VerveStacks_SVK_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_SVK_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SVK_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B7D10FE-AE69-43FE-862B-158249B7EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D5D4EEA-1EA6-4533-9CB5-6F5E418C387B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -908,9 +908,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -948,7 +948,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1054,7 +1054,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1196,7 +1196,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1649,7 +1649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9474BFD0-14B2-43DA-8642-3AB39DA2C591}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3132969D-9A0C-4303-BE7E-A285D9BA964C}">
   <dimension ref="B9:E87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
